--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED16.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED16.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>83W</t>
+          <t>192W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -831,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N4"/>
+  <dimension ref="B2:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -917,18 +917,6 @@
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>贷款时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1季</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>74W</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1572,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>busy</t>
+          <t>ready</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1712,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-3-0114</t>
+          <t>SIM_XA_FIXED-2-0068</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1726,11 +1714,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33W</t>
+          <t>77W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1740,12 +1728,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>第3年</t>
+          <t>第2年</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4季</t>
+          <t>5季</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1760,14 +1748,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-4-0024</t>
+          <t>SIM_XA_FIXED-4-0138</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1781,11 +1769,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>74W</t>
+          <t>61W</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1805,7 +1793,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2季</t>
+          <t>4季</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1815,7 +1803,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>第5年3季</t>
+          <t>第4年4季</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G55"/>
+  <dimension ref="B2:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -1957,7 +1945,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>production_line_ordered | {"line": {"accumulated_depreciation_wan": 40.0, "book_value_wan": 0.0, "cost_wan": 40.0, "line_id": "L-f5cb9dbb14", "line_type": "手工线", "maintenance_wan_per_year": 15.0, "ownership": "purchased", "product_id": "P1", "remaining_install_quarters": 0, "status": "busy"}}</t>
+          <t>production_line_ordered | {"line": {"accumulated_depreciation_wan": 40.0, "book_value_wan": 0.0, "cost_wan": 40.0, "line_id": "L-f5cb9dbb14", "line_type": "手工线", "maintenance_wan_per_year": 15.0, "ownership": "purchased", "product_id": "P1", "remaining_install_quarters": 0, "status": "ready"}}</t>
         </is>
       </c>
     </row>
@@ -2153,10 +2141,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="E14" t="n">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2165,7 +2153,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2170,7 @@
         <v>-14</v>
       </c>
       <c r="E15" t="n">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2208,7 +2196,7 @@
         <v>-14</v>
       </c>
       <c r="E16" t="n">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2234,7 +2222,7 @@
         <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2260,7 +2248,7 @@
         <v>-14</v>
       </c>
       <c r="E18" t="n">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2286,7 +2274,7 @@
         <v>-15</v>
       </c>
       <c r="E19" t="n">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2312,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2338,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2357,14 +2345,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-8</v>
+        <v>-24</v>
       </c>
       <c r="E22" t="n">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2373,7 +2361,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
         </is>
       </c>
     </row>
@@ -2383,14 +2371,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="E23" t="n">
-        <v>391</v>
+        <v>369</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2399,7 +2387,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-1f67285bd6", "line_id": "L-f5cb9dbb14", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2409,23 +2397,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-12</v>
       </c>
       <c r="E24" t="n">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2435,23 +2423,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="E25" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-642d26e993", "line_id": "L-f5cb9dbb14", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2456,7 @@
         <v>-14</v>
       </c>
       <c r="E26" t="n">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2487,14 +2475,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2503,7 +2491,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 40.0, "order_id": "SIM_XA_FIXED-2-0068", "receivable_term_quarters": 2, "revenue_wan": 77.0}</t>
         </is>
       </c>
     </row>
@@ -2513,23 +2501,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="E28" t="n">
-        <v>343</v>
+        <v>305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-3-0114", "receivable_term_quarters": 2, "revenue_wan": 33.0}</t>
+          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
         </is>
       </c>
     </row>
@@ -2539,23 +2527,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-12</v>
+        <v>-16</v>
       </c>
       <c r="E29" t="n">
-        <v>331</v>
+        <v>289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-10cfdec288", "line_id": "L-f5cb9dbb14", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2565,23 +2553,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="E30" t="n">
-        <v>323</v>
+        <v>275</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-cdb635f429", "line_id": "L-f5cb9dbb14", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2586,7 @@
         <v>-14</v>
       </c>
       <c r="E31" t="n">
-        <v>309</v>
+        <v>261</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2617,14 +2605,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-15</v>
+        <v>77</v>
       </c>
       <c r="E32" t="n">
-        <v>294</v>
+        <v>338</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2633,7 +2621,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-f5cb9dbb14"}</t>
+          <t>receivable_collected | {"receivable_id": "AR-7a23c40626"}</t>
         </is>
       </c>
     </row>
@@ -2643,14 +2631,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E33" t="n">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2659,7 +2647,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-f5cb9dbb14", "asset_type": "factory"}</t>
+          <t>maintenance_expense | {"line_id": "L-f5cb9dbb14"}</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2685,7 +2673,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-f5cb9dbb14", "asset_type": "production_line"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-f5cb9dbb14", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2695,23 +2683,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>286</v>
+        <v>323</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-f5cb9dbb14", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2721,14 +2709,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="E36" t="n">
-        <v>272</v>
+        <v>311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2737,7 +2725,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -2747,14 +2735,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>33</v>
+        <v>-14</v>
       </c>
       <c r="E37" t="n">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2763,7 +2751,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-54abf98f83"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2768,7 @@
         <v>-14</v>
       </c>
       <c r="E38" t="n">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2806,7 +2794,7 @@
         <v>-14</v>
       </c>
       <c r="E39" t="n">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2825,14 +2813,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2841,7 +2829,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 40.0, "order_id": "SIM_XA_FIXED-4-0138", "receivable_term_quarters": 4, "revenue_wan": 61.0}</t>
         </is>
       </c>
     </row>
@@ -2851,14 +2839,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-15</v>
+        <v>-24</v>
       </c>
       <c r="E41" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2867,7 +2855,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-f5cb9dbb14"}</t>
+          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
         </is>
       </c>
     </row>
@@ -2877,14 +2865,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="E42" t="n">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2893,7 +2881,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-f5cb9dbb14", "asset_type": "factory"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-fb3bd23143", "line_id": "L-f5cb9dbb14", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2903,14 +2891,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E43" t="n">
-        <v>248</v>
+        <v>215</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2919,7 +2907,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-f5cb9dbb14", "asset_type": "production_line"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2929,23 +2917,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-24</v>
+        <v>-15</v>
       </c>
       <c r="E44" t="n">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
+          <t>maintenance_expense | {"line_id": "L-f5cb9dbb14"}</t>
         </is>
       </c>
     </row>
@@ -2955,23 +2943,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-c3bfa550cc", "line_id": "L-f5cb9dbb14", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-f5cb9dbb14", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2981,23 +2969,23 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>200</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-f5cb9dbb14", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -3007,14 +2995,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="E47" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3023,7 +3011,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -3040,11 +3028,11 @@
         <v>-14</v>
       </c>
       <c r="E48" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3059,23 +3047,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E49" t="n">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>第5年3季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 60.0, "order_id": "SIM_XA_FIXED-4-0024", "receivable_term_quarters": 2, "revenue_wan": 74.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3085,14 +3073,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-36</v>
+        <v>-14</v>
       </c>
       <c r="E50" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3101,7 +3089,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3111,14 +3099,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-24</v>
+        <v>61</v>
       </c>
       <c r="E51" t="n">
-        <v>112</v>
+        <v>207</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3127,7 +3115,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-30e4bb2ac8", "line_id": "L-f5cb9dbb14", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 1}}</t>
+          <t>receivable_collected | {"receivable_id": "AR-981062479b"}</t>
         </is>
       </c>
     </row>
@@ -3137,23 +3125,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E52" t="n">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>第5年3季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-f5cb9dbb14"}</t>
         </is>
       </c>
     </row>
@@ -3163,14 +3151,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3179,7 +3167,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-f5cb9dbb14"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-f5cb9dbb14", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3204,32 +3192,6 @@
         </is>
       </c>
       <c r="G54" t="inlineStr">
-        <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-f5cb9dbb14", "asset_type": "factory"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="n">
-        <v>52</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>83</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-f5cb9dbb14", "asset_type": "production_line"}</t>
         </is>
@@ -3336,16 +3298,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -3561,16 +3523,16 @@
         <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G13" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H13" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -3626,13 +3588,13 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="H16" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3651,13 +3613,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3676,13 +3638,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3698,16 +3660,16 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G19" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H19" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -3723,16 +3685,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-79</v>
+        <v>-83</v>
       </c>
       <c r="F20" t="n">
-        <v>-66</v>
+        <v>-46</v>
       </c>
       <c r="G20" t="n">
-        <v>-79</v>
+        <v>-62</v>
       </c>
       <c r="H20" t="n">
-        <v>-51</v>
+        <v>-69</v>
       </c>
     </row>
     <row r="21">
@@ -3773,16 +3735,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-94.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-81.2</v>
+        <v>-61.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-94.2</v>
+        <v>-77.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-66.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="23">
@@ -3823,16 +3785,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-94.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-81.2</v>
+        <v>-61.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-94.2</v>
+        <v>-77.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-66.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="25">
@@ -3873,16 +3835,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-94.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-81.2</v>
+        <v>-61.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-94.2</v>
+        <v>-77.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-66.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="28">
@@ -3972,16 +3934,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F30" t="n">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="G30" t="n">
-        <v>248</v>
+        <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>83</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31">
@@ -4000,13 +3962,13 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="H31" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4025,13 +3987,13 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4050,13 +4012,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
@@ -4097,16 +4059,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F35" t="n">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="G35" t="n">
-        <v>268</v>
+        <v>301</v>
       </c>
       <c r="H35" t="n">
-        <v>217</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36">
@@ -4222,16 +4184,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>494.6</v>
+        <v>490.6</v>
       </c>
       <c r="F40" t="n">
-        <v>413.4</v>
+        <v>429.4</v>
       </c>
       <c r="G40" t="n">
-        <v>319.2</v>
+        <v>352.2</v>
       </c>
       <c r="H40" t="n">
-        <v>253</v>
+        <v>268</v>
       </c>
     </row>
     <row r="41">
@@ -4400,13 +4362,13 @@
         <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-180.4</v>
+        <v>-184.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-261.6</v>
+        <v>-245.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-355.8</v>
+        <v>-322.8</v>
       </c>
     </row>
     <row r="48">
@@ -4422,16 +4384,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-94.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-81.2</v>
+        <v>-61.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-94.2</v>
+        <v>-77.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-66.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="49">
@@ -4447,16 +4409,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>494.6</v>
+        <v>490.6</v>
       </c>
       <c r="F49" t="n">
-        <v>413.4</v>
+        <v>429.4</v>
       </c>
       <c r="G49" t="n">
-        <v>319.2</v>
+        <v>352.2</v>
       </c>
       <c r="H49" t="n">
-        <v>253</v>
+        <v>268</v>
       </c>
     </row>
     <row r="50">
@@ -4472,16 +4434,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>494.6</v>
+        <v>490.6</v>
       </c>
       <c r="F50" t="n">
-        <v>413.4</v>
+        <v>429.4</v>
       </c>
       <c r="G50" t="n">
-        <v>319.2</v>
+        <v>352.2</v>
       </c>
       <c r="H50" t="n">
-        <v>253</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -4552,7 +4514,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4701,7 +4663,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -4850,7 +4812,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4999,7 +4961,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -5148,7 +5110,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
